--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02E45500-ECD7-4162-9F4B-ABD8408F27F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7693039-51C9-4D25-BEAF-2027F9A2152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7693039-51C9-4D25-BEAF-2027F9A2152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{362517B5-B71F-4188-AC65-AC207E91C89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>

--- a/src/xleda/assets/xleda_template.xlsx
+++ b/src/xleda/assets/xleda_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\xleda\src\xleda\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{362517B5-B71F-4188-AC65-AC207E91C89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F47CCAFE-FAC8-4427-B3E0-FA58CCA40D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{040F3586-419E-4585-8ACE-6588AD7C95BD}"/>
   </bookViews>
